--- a/result/train_info_googlenet_part_detrend_plr_stft_bin_win_lcc.xlsx
+++ b/result/train_info_googlenet_part_detrend_plr_stft_bin_win_lcc.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4228880041310727</v>
+        <v>0.4254355377242257</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3084978172941321</v>
+        <v>0.2532529159719069</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8647342995169082</v>
+        <v>0.8978075065031587</v>
       </c>
       <c r="F2" t="n">
-        <v>0.951007326007326</v>
+        <v>0.9265289912629071</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7698295033358044</v>
+        <v>0.8647146034099333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.850880786562884</v>
+        <v>0.8945552147239264</v>
       </c>
       <c r="I2" t="n">
-        <v>70.58493709564209</v>
+        <v>47.97849011421204</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2061872176278001</v>
+        <v>0.1901945203520568</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1403074289104466</v>
+        <v>0.1416380266829796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9464882943143813</v>
+        <v>0.9451876625789669</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9725490196078431</v>
+        <v>0.9807923169267707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9191994069681245</v>
+        <v>0.9084507042253521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9451219512195121</v>
+        <v>0.9432364825861074</v>
       </c>
       <c r="I3" t="n">
-        <v>71.05679535865784</v>
+        <v>47.19006180763245</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1037724430044562</v>
+        <v>0.09427761360670801</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07146584584319843</v>
+        <v>0.08151362786488332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9738015607580826</v>
+        <v>0.9682274247491639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9681435371658733</v>
+        <v>0.9813333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9799851742031134</v>
+        <v>0.9547813194959229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9740283661816173</v>
+        <v>0.9678752583129814</v>
       </c>
       <c r="I4" t="n">
-        <v>71.90481305122375</v>
+        <v>47.26716017723083</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06736235107249548</v>
+        <v>0.06074252201712664</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05201624431674914</v>
+        <v>0.05815800032909055</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9819769602378298</v>
+        <v>0.9801189149015236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9811320754716981</v>
+        <v>0.9702359346642468</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.98204036289576</v>
+        <v>0.9803777737025491</v>
       </c>
       <c r="I5" t="n">
-        <v>72.29387044906616</v>
+        <v>47.33759307861328</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04831388949533858</v>
+        <v>0.04404201609031318</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04595675371303471</v>
+        <v>0.0350944977963189</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9849498327759197</v>
+        <v>0.9873652917131178</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9815973500184026</v>
+        <v>0.9866765358993338</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9885100074128984</v>
+        <v>0.9881393624907339</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9850415512465374</v>
+        <v>0.9874074074074074</v>
       </c>
       <c r="I6" t="n">
-        <v>72.44569969177246</v>
+        <v>52.09691643714905</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03500294756272463</v>
+        <v>0.03425682194309204</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06580626754298222</v>
+        <v>0.03373381173112099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9797473058342624</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9861058956064589</v>
+        <v>0.9878048780487805</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9733135656041513</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9796679723932102</v>
+        <v>0.9892672094744633</v>
       </c>
       <c r="I7" t="n">
-        <v>72.99595713615417</v>
+        <v>49.9281849861145</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03513024812273648</v>
+        <v>0.0316570657122061</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04285423895661009</v>
+        <v>0.03111657005846335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.986250464511334</v>
+        <v>0.9897807506503159</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9880952380952381</v>
+        <v>0.9896257873286403</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9844329132690882</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9862606758262161</v>
+        <v>0.9898091532332778</v>
       </c>
       <c r="I8" t="n">
-        <v>73.16682529449463</v>
+        <v>48.15037298202515</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02697129703913386</v>
+        <v>0.02779992127464635</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06630744059988954</v>
+        <v>0.04530763952733161</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9803047194351542</v>
+        <v>0.9832775919732442</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9747252747252747</v>
+        <v>0.9883895131086142</v>
       </c>
       <c r="G9" t="n">
-        <v>0.986286137879911</v>
+        <v>0.9781319495922906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9804716285924834</v>
+        <v>0.9832339791356185</v>
       </c>
       <c r="I9" t="n">
-        <v>72.99599933624268</v>
+        <v>45.96161890029907</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02655351254511725</v>
+        <v>0.02201485313458223</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04364054763639954</v>
+        <v>0.02467106009255571</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9851356373095503</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9866171003717472</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9851521900519673</v>
+        <v>0.9903988183161004</v>
       </c>
       <c r="I10" t="n">
-        <v>73.63821625709534</v>
+        <v>49.77710723876953</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02832334163330122</v>
+        <v>0.01798502500313633</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04134102532510596</v>
+        <v>0.02340295854000996</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9869936826458565</v>
+        <v>0.9938684503901896</v>
       </c>
       <c r="F11" t="n">
-        <v>0.97677793904209</v>
+        <v>0.993701370878103</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9871653832049871</v>
+        <v>0.9938854919399667</v>
       </c>
       <c r="I11" t="n">
-        <v>72.57541012763977</v>
+        <v>48.90626525878906</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01734429731791696</v>
+        <v>0.02445063848317605</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08220243732308551</v>
+        <v>0.03144995923744399</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9756596060943887</v>
+        <v>0.9894091415830546</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9540148567385921</v>
+        <v>0.9943841257955822</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9996293550778355</v>
+        <v>0.9844329132690882</v>
       </c>
       <c r="H12" t="n">
-        <v>0.976289592760181</v>
+        <v>0.9893834978580741</v>
       </c>
       <c r="I12" t="n">
-        <v>72.81948590278625</v>
+        <v>47.70407485961914</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01780859382644854</v>
+        <v>0.01940088791653454</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03749198645093105</v>
+        <v>0.02692655296655256</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9868078781122259</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9969731365872115</v>
+        <v>0.9914688427299704</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9766493699036323</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9867066092492043</v>
+        <v>0.9911012235817576</v>
       </c>
       <c r="I13" t="n">
-        <v>72.45085620880127</v>
+        <v>47.23807168006897</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01840158469200067</v>
+        <v>0.01817821509244244</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03357122845551397</v>
+        <v>0.02466570966509457</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9896065330363771</v>
+        <v>0.9918639053254438</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9881393624907339</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9888724035608308</v>
+        <v>0.9929655683080341</v>
       </c>
       <c r="I14" t="n">
-        <v>72.03151535987854</v>
+        <v>47.24536490440369</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01854132744864205</v>
+        <v>0.01795306638712883</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03597612923631836</v>
+        <v>0.02724366185937997</v>
       </c>
       <c r="E15" t="n">
-        <v>0.989223337049424</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9929051530993278</v>
+        <v>0.9874861980125138</v>
       </c>
       <c r="G15" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9892113095238095</v>
+        <v>0.9909510618651893</v>
       </c>
       <c r="I15" t="n">
-        <v>72.2344856262207</v>
+        <v>43.13514041900635</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01504099066098955</v>
+        <v>0.01758034348546754</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07192541296423699</v>
+        <v>0.040177390623091</v>
       </c>
       <c r="E16" t="n">
-        <v>0.979933110367893</v>
+        <v>0.9875510962467484</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9839312406576981</v>
+        <v>0.9852452969383991</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9759080800593032</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9799032378116859</v>
+        <v>0.9876132371972638</v>
       </c>
       <c r="I16" t="n">
-        <v>72.02191615104675</v>
+        <v>42.6060996055603</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01651341544798211</v>
+        <v>0.01523559786565117</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02564213812372237</v>
+        <v>0.02975077466514325</v>
       </c>
       <c r="E17" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9918276374442794</v>
+        <v>0.9893067846607669</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9896219421793921</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9907235621521335</v>
+        <v>0.9918669131238448</v>
       </c>
       <c r="I17" t="n">
-        <v>72.03420877456665</v>
+        <v>42.28052425384521</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01171390004315659</v>
+        <v>0.01402242859269103</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.04619800554417603</v>
+        <v>0.04966639557725215</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9882943143812709</v>
+        <v>0.9836492010405053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9827775742030047</v>
+        <v>0.9714595375722543</v>
       </c>
       <c r="G18" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.988391376451078</v>
+        <v>0.9839004756677644</v>
       </c>
       <c r="I18" t="n">
-        <v>72.34495568275452</v>
+        <v>42.74430894851685</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.014723914451714</v>
+        <v>0.01274694843619865</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03373218127413544</v>
+        <v>0.03147437008006151</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9824497257769652</v>
+        <v>0.9903917220990391</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9891404380636849</v>
+        <v>0.9918578830495929</v>
       </c>
       <c r="I19" t="n">
-        <v>72.16462969779968</v>
+        <v>42.58592796325684</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01177325114265052</v>
+        <v>0.01302854635190586</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02154036900589567</v>
+        <v>0.03164745900833692</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9940718784735088</v>
+        <v>0.9885651051272594</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9942560681860293</v>
+        <v>0.9909410242188944</v>
       </c>
       <c r="I20" t="n">
-        <v>72.82727670669556</v>
+        <v>42.83606624603271</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.008356168465049421</v>
+        <v>0.01387801646387675</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03026122114856689</v>
+        <v>0.04521359873370036</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9871794871794872</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9882482556004407</v>
+        <v>0.9802703690171721</v>
       </c>
       <c r="G21" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9928057553956835</v>
+        <v>0.9873045078196873</v>
       </c>
       <c r="I21" t="n">
-        <v>72.73039269447327</v>
+        <v>42.42420125007629</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01471781283766701</v>
+        <v>0.01144607837945375</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04126135767173172</v>
+        <v>0.01939651138806535</v>
       </c>
       <c r="E22" t="n">
-        <v>0.986250464511334</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9834193072955048</v>
+        <v>0.9937037037037038</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9892512972572276</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9863266814486327</v>
+        <v>0.9940718784735088</v>
       </c>
       <c r="I22" t="n">
-        <v>74.00059533119202</v>
+        <v>42.71850490570068</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01172884778603923</v>
+        <v>0.009463162895468029</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02806066438374486</v>
+        <v>0.03075147140792677</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9889786921381337</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9933579335793358</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="I23" t="n">
-        <v>73.72922468185425</v>
+        <v>42.99484825134277</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.007942128951659798</v>
+        <v>0.009419059724799563</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.05467453239208016</v>
+        <v>0.01333140208720923</v>
       </c>
       <c r="E24" t="n">
-        <v>0.986250464511334</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9936042136945071</v>
+        <v>0.9940893978574067</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9788732394366197</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H24" t="n">
-        <v>0.986183719193428</v>
+        <v>0.9957446808510638</v>
       </c>
       <c r="I24" t="n">
-        <v>73.56019020080566</v>
+        <v>42.35887122154236</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01227789842832079</v>
+        <v>0.01276144669042877</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03932555147275169</v>
+        <v>0.02876238489855727</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9847640282422891</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9973384030418251</v>
+        <v>0.9900110987791343</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9722016308376575</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9846096096096096</v>
+        <v>0.9909276059988891</v>
       </c>
       <c r="I25" t="n">
-        <v>73.08864545822144</v>
+        <v>42.63164091110229</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01115906692894054</v>
+        <v>0.006629311292855984</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02811309151019427</v>
+        <v>0.01970446787867299</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.9942400594574508</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9903774981495189</v>
+        <v>0.9951726698848867</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9911111111111112</v>
+        <v>0.9942496753849007</v>
       </c>
       <c r="I26" t="n">
-        <v>73.07953882217407</v>
+        <v>42.49661231040955</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.008834105326701133</v>
+        <v>0.007152413850074645</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02481292758777014</v>
+        <v>0.02744859251852284</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9896869244935543</v>
+        <v>0.9918306721128852</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9927951228523924</v>
+        <v>0.9909107772212947</v>
       </c>
       <c r="I27" t="n">
-        <v>72.61036348342896</v>
+        <v>42.51024699211121</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.008499833033296898</v>
+        <v>0.00918306527192587</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03271916683253475</v>
+        <v>0.02781914686426808</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9920104050538833</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9966329966329966</v>
+        <v>0.9885651051272594</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9873980726464048</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9919940420778254</v>
+        <v>0.9909410242188944</v>
       </c>
       <c r="I28" t="n">
-        <v>72.44871425628662</v>
+        <v>42.35454893112183</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.005703959614881405</v>
+        <v>0.00825559783314839</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0259114768682728</v>
+        <v>0.0292710939372911</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9929603556872916</v>
+        <v>0.9929315476190477</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9892512972572276</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9931443394478414</v>
+        <v>0.9910880059413294</v>
       </c>
       <c r="I29" t="n">
-        <v>72.33786201477051</v>
+        <v>42.54183793067932</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.007623140264149291</v>
+        <v>0.004806557034490054</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03074543844847685</v>
+        <v>0.0177000575079078</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9900698786318499</v>
+        <v>0.9937130177514792</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9939080671958649</v>
+        <v>0.994816734542762</v>
       </c>
       <c r="I30" t="n">
-        <v>72.14201855659485</v>
+        <v>42.76364088058472</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.005322606520057564</v>
+        <v>0.009492786855776744</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02589037603419343</v>
+        <v>0.03817231064908945</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9895949461166852</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9875412238915353</v>
+        <v>0.9831748354059985</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9931822369633315</v>
+        <v>0.9896907216494846</v>
       </c>
       <c r="I31" t="n">
-        <v>72.29257106781006</v>
+        <v>42.43087983131409</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.009945306989747877</v>
+        <v>0.01066136360356032</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0246364905490053</v>
+        <v>0.02205832641061668</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9922394678492239</v>
+        <v>0.9911471781630394</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9937083641746854</v>
+        <v>0.9935293030134961</v>
       </c>
       <c r="I32" t="n">
-        <v>72.13822674751282</v>
+        <v>42.71331453323364</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.003425649610582282</v>
+        <v>0.005887847577860981</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01793616897300486</v>
+        <v>0.02527609958030805</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9955406911928651</v>
+        <v>0.9910813823857302</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9940872135994088</v>
+        <v>0.9966266866566716</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.985544848035582</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9955588452997779</v>
+        <v>0.9910547894148342</v>
       </c>
       <c r="I33" t="n">
-        <v>71.92618227005005</v>
+        <v>42.65657472610474</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.006156949558200241</v>
+        <v>0.004190199922010751</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0299850183732788</v>
+        <v>0.01702181048233275</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9923820141211446</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F34" t="n">
-        <v>0.990764684152198</v>
+        <v>0.9955506117908788</v>
       </c>
       <c r="G34" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9924144310823312</v>
+        <v>0.9953660797034291</v>
       </c>
       <c r="I34" t="n">
-        <v>71.76750135421753</v>
+        <v>42.6807165145874</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.00470756310537642</v>
+        <v>0.005198127873840968</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03843502831420111</v>
+        <v>0.02463978752417224</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9888517279821628</v>
+        <v>0.9927536231884058</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9799854439592431</v>
+        <v>0.9907715023994094</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9889827396254132</v>
+        <v>0.9927871277972998</v>
       </c>
       <c r="I35" t="n">
-        <v>72.07151794433594</v>
+        <v>42.48145246505737</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.008868059034403594</v>
+        <v>0.008963141219428939</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01916597525173771</v>
+        <v>0.03104637890259223</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9940674823878384</v>
+        <v>0.9936708860759493</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9892512972572276</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9938832252085265</v>
+        <v>0.9914561664190193</v>
       </c>
       <c r="I36" t="n">
-        <v>71.74676489830017</v>
+        <v>42.63382959365845</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.004987069584617536</v>
+        <v>0.007121494242055038</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.02018065044843935</v>
+        <v>0.02651645891279183</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.992196209587514</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9926117473217584</v>
+        <v>0.9911242603550295</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9942645698427383</v>
+        <v>0.9922251018141429</v>
       </c>
       <c r="I37" t="n">
-        <v>71.85097742080688</v>
+        <v>42.57216238975525</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.004642013826703806</v>
+        <v>0.00458524285618208</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03109745126077014</v>
+        <v>0.02177238359340582</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9912671869193609</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9860652731939861</v>
+        <v>0.9904270986745214</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9913364055299539</v>
+        <v>0.9937199852234947</v>
       </c>
       <c r="I38" t="n">
-        <v>71.43318223953247</v>
+        <v>42.32824611663818</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.005140610799023062</v>
+        <v>0.004219732227419252</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.02704148209501839</v>
+        <v>0.02914842225683065</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9900552486187846</v>
+        <v>0.9922193404964802</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9931646037317569</v>
+        <v>0.9924031869557162</v>
       </c>
       <c r="I39" t="n">
-        <v>71.52273774147034</v>
+        <v>42.60926103591919</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.005837975153462103</v>
+        <v>0.005454199460228715</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.02794235644648039</v>
+        <v>0.01997205239942193</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9914529914529915</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9925705794947994</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9914656771799629</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="I40" t="n">
-        <v>71.56794714927673</v>
+        <v>42.35804986953735</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.004483497967711146</v>
+        <v>0.002178028126234746</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02107231825590058</v>
+        <v>0.03643974869291709</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9915160457395795</v>
+        <v>0.9922193404964802</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9938990571270105</v>
+        <v>0.9924031869557162</v>
       </c>
       <c r="I41" t="n">
-        <v>71.47784280776978</v>
+        <v>42.70506405830383</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.001534600444060365</v>
+        <v>0.006435152947449516</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0159758370968902</v>
+        <v>0.02097440912630245</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9966555183946488</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9959289415247965</v>
+        <v>0.9955440029706647</v>
       </c>
       <c r="G42" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9966666666666667</v>
+        <v>0.9946206640697459</v>
       </c>
       <c r="I42" t="n">
-        <v>71.63564157485962</v>
+        <v>42.13139867782593</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.002717543025122902</v>
+        <v>0.003281159577815498</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02607645869743492</v>
+        <v>0.02168993852243126</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9922566371681416</v>
+        <v>0.9966505396352809</v>
       </c>
       <c r="G43" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9948243992606285</v>
+        <v>0.9946146703806871</v>
       </c>
       <c r="I43" t="n">
-        <v>71.84497022628784</v>
+        <v>42.90828514099121</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.002270629369401262</v>
+        <v>0.003994314807910039</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02299353817657719</v>
+        <v>0.02153393827002596</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9940959409594096</v>
+        <v>0.992619926199262</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9963017751479289</v>
+        <v>0.9948224852071006</v>
       </c>
       <c r="I44" t="n">
-        <v>71.96488547325134</v>
+        <v>42.56161236763</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.001624359828660472</v>
+        <v>0.0006964962125889873</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02193659130888639</v>
+        <v>0.0183800624444095</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9940915805022157</v>
+        <v>0.9937199852234947</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9959304476507584</v>
+        <v>0.9953746530989824</v>
       </c>
       <c r="I45" t="n">
-        <v>71.6017050743103</v>
+        <v>42.58107972145081</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.007318267790954979</v>
+        <v>0.0007110740162958534</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01662672140625045</v>
+        <v>0.02437673904356865</v>
       </c>
       <c r="E46" t="n">
         <v>0.9947974730583427</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9951780415430267</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9948090470893586</v>
       </c>
       <c r="I46" t="n">
-        <v>71.21341061592102</v>
+        <v>42.51250624656677</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.002650790815106927</v>
+        <v>0.0009329007191486084</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.02133031658762474</v>
+        <v>0.02630714567606086</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9940542549238202</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9929733727810651</v>
+        <v>0.9944175660588016</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9903632320237212</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9940762680488708</v>
+        <v>0.9923862581244197</v>
       </c>
       <c r="I47" t="n">
-        <v>71.20053362846375</v>
+        <v>42.60229253768921</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.003568984166547407</v>
+        <v>0.007665806985524549</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01357754438778269</v>
+        <v>0.01822034029352765</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9944506104328524</v>
+        <v>0.9944465012958164</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9953712275504536</v>
+        <v>0.9949990739025746</v>
       </c>
       <c r="I48" t="n">
-        <v>71.6387767791748</v>
+        <v>42.48900842666626</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0007713336292474458</v>
+        <v>0.005690102532535796</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01272636500669562</v>
+        <v>0.02108532550125438</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9948320413436692</v>
+        <v>0.9911373707533235</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9988880652335063</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9968559275013871</v>
+        <v>0.9929707732149463</v>
       </c>
       <c r="I49" t="n">
-        <v>71.04243612289429</v>
+        <v>42.31620025634766</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7.242188838317897e-05</v>
+        <v>0.001913184363199919</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0113653824832586</v>
+        <v>0.01903723985617153</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9963004069552349</v>
+        <v>0.9926280869885735</v>
       </c>
       <c r="G50" t="n">
         <v>0.9981467753891772</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9972227365302722</v>
+        <v>0.9953797819257069</v>
       </c>
       <c r="I50" t="n">
-        <v>70.99709177017212</v>
+        <v>42.63324618339539</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001119884566684257</v>
+        <v>0.001992401737798423</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01994916235720445</v>
+        <v>0.0153053836394178</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9955456570155902</v>
+        <v>0.9977686872443288</v>
       </c>
       <c r="G51" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H51" t="n">
-        <v>0.994807121661721</v>
+        <v>0.9961017263783182</v>
       </c>
       <c r="I51" t="n">
-        <v>70.9583146572113</v>
+        <v>42.44104146957397</v>
       </c>
     </row>
   </sheetData>
